--- a/docs/cadrage/equipe-09-release-planning-v3.0.xlsx
+++ b/docs/cadrage/equipe-09-release-planning-v3.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" state="visible" r:id="rId3"/>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Statut</t>
   </si>
   <si>
-    <t xml:space="preserve">En revue PO</t>
+    <t xml:space="preserve">Validé</t>
   </si>
   <si>
     <t xml:space="preserve">💡 Convention de nommage du fichier :</t>
@@ -844,196 +844,200 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1292,42 +1296,42 @@
   <dimension ref="B2:B21"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="85.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1350,76 +1354,76 @@
   <dimension ref="B2:C13"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="63.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="63.67"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1442,368 +1446,368 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="19" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="22" t="n">
         <v>17.5</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="24" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="28" t="n">
         <v>17.5</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="27" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="24" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="28" t="n">
         <v>17.5</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="H15" s="30" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="28" t="n">
         <v>17.5</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="27" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="30" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="34" t="n">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="35" t="n">
         <v>145</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1826,204 +1830,204 @@
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="44" t="n">
         <v>16</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="44" t="n">
         <v>16</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="43" t="n">
+      <c r="C12" s="44" t="n">
         <v>24</v>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="44" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="44" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="44" t="n">
         <v>32</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="44" t="n">
         <v>32</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="44" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="43" t="n">
+      <c r="C14" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="44" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C15" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="44" t="n">
         <v>48</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="44" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="43" t="n">
+      <c r="C16" s="44" t="n">
         <v>56</v>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="44" t="n">
         <v>56</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="44" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2046,130 +2050,130 @@
   <dimension ref="A2:D14"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="149.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="149.22"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="47" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="47" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="47" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="47" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="47" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="47" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="47" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="48" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="47" t="s">
         <v>156</v>
       </c>
     </row>
